--- a/BUT2/1-DOC/SemestreBUT2_RA_complete.xlsx
+++ b/BUT2/1-DOC/SemestreBUT2_RA_complete.xlsx
@@ -812,30 +812,6 @@
     <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -876,6 +852,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1192,48 +1192,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="40"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="54"/>
     </row>
     <row r="2" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="40"/>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="40"/>
+      <c r="A2" s="54"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="54"/>
+      <c r="Q2" s="54"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="40"/>
-      <c r="B3" s="40"/>
+      <c r="A3" s="54"/>
+      <c r="B3" s="54"/>
       <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1255,7 +1255,7 @@
       <c r="I3" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="J3" s="40"/>
+      <c r="J3" s="54"/>
       <c r="K3" s="3" t="s">
         <v>58</v>
       </c>
@@ -1274,58 +1274,58 @@
       <c r="P3" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="Q3" s="40"/>
+      <c r="Q3" s="54"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="40"/>
-      <c r="B4" s="40"/>
+      <c r="A4" s="54"/>
+      <c r="B4" s="54"/>
       <c r="C4" s="32"/>
-      <c r="D4" s="47">
+      <c r="D4" s="39">
         <f>C4</f>
         <v>0</v>
       </c>
-      <c r="E4" s="48">
+      <c r="E4" s="40">
         <f>C4</f>
         <v>0</v>
       </c>
-      <c r="F4" s="48">
+      <c r="F4" s="40">
         <f>C4</f>
         <v>0</v>
       </c>
-      <c r="G4" s="48">
+      <c r="G4" s="40">
         <f>C4</f>
         <v>0</v>
       </c>
-      <c r="H4" s="48">
+      <c r="H4" s="40">
         <f>C4</f>
         <v>0</v>
       </c>
-      <c r="I4" s="49">
+      <c r="I4" s="41">
         <f>C4</f>
         <v>0</v>
       </c>
-      <c r="J4" s="40"/>
+      <c r="J4" s="54"/>
       <c r="K4" s="12"/>
       <c r="L4" s="13"/>
       <c r="M4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
       <c r="P4" s="14"/>
-      <c r="Q4" s="40"/>
+      <c r="Q4" s="54"/>
       <c r="S4" s="31" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="41"/>
-      <c r="B5" s="41"/>
+      <c r="A5" s="55"/>
+      <c r="B5" s="55"/>
       <c r="C5" s="37"/>
       <c r="D5" s="20">
         <f>(D4*K5)/K5</f>
         <v>0</v>
       </c>
       <c r="E5" s="21">
-        <f t="shared" ref="D5:I5" si="0">(E4*L5)/L5</f>
+        <f t="shared" ref="E5:I5" si="0">(E4*L5)/L5</f>
         <v>0</v>
       </c>
       <c r="F5" s="21">
@@ -1344,7 +1344,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J5" s="40"/>
+      <c r="J5" s="54"/>
       <c r="K5" s="17">
         <v>40</v>
       </c>
@@ -1363,7 +1363,7 @@
       <c r="P5" s="19">
         <v>40</v>
       </c>
-      <c r="Q5" s="40"/>
+      <c r="Q5" s="54"/>
     </row>
     <row r="6" spans="1:19" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -1372,21 +1372,21 @@
       <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="43"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="42"/>
-      <c r="M6" s="42"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="42"/>
-      <c r="P6" s="42"/>
-      <c r="Q6" s="40"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="56"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="56"/>
+      <c r="N6" s="56"/>
+      <c r="O6" s="56"/>
+      <c r="P6" s="56"/>
+      <c r="Q6" s="54"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="H7" s="27"/>
       <c r="I7" s="28"/>
-      <c r="J7" s="40"/>
+      <c r="J7" s="54"/>
       <c r="K7" s="12">
         <v>15</v>
       </c>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="O7" s="13"/>
       <c r="P7" s="14"/>
-      <c r="Q7" s="40"/>
+      <c r="Q7" s="54"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -1451,7 +1451,7 @@
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="26"/>
-      <c r="J8" s="40"/>
+      <c r="J8" s="54"/>
       <c r="K8" s="15">
         <v>10</v>
       </c>
@@ -1462,7 +1462,7 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="16"/>
-      <c r="Q8" s="40"/>
+      <c r="Q8" s="54"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -1487,7 +1487,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="26"/>
-      <c r="J9" s="40"/>
+      <c r="J9" s="54"/>
       <c r="K9" s="15">
         <v>12</v>
       </c>
@@ -1500,7 +1500,7 @@
         <v>10</v>
       </c>
       <c r="P9" s="16"/>
-      <c r="Q9" s="40"/>
+      <c r="Q9" s="54"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -1525,7 +1525,7 @@
         <f>B10</f>
         <v>0</v>
       </c>
-      <c r="J10" s="40"/>
+      <c r="J10" s="54"/>
       <c r="K10" s="15">
         <v>15</v>
       </c>
@@ -1538,7 +1538,7 @@
       <c r="P10" s="16">
         <v>5</v>
       </c>
-      <c r="Q10" s="40"/>
+      <c r="Q10" s="54"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -1557,7 +1557,7 @@
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
       <c r="I11" s="26"/>
-      <c r="J11" s="40"/>
+      <c r="J11" s="54"/>
       <c r="K11" s="15"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1">
@@ -1566,7 +1566,7 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="16"/>
-      <c r="Q11" s="40"/>
+      <c r="Q11" s="54"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -1588,7 +1588,7 @@
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="26"/>
-      <c r="J12" s="40"/>
+      <c r="J12" s="54"/>
       <c r="K12" s="15"/>
       <c r="L12" s="1">
         <v>5</v>
@@ -1599,7 +1599,7 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="16"/>
-      <c r="Q12" s="40"/>
+      <c r="Q12" s="54"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="26"/>
-      <c r="J13" s="40"/>
+      <c r="J13" s="54"/>
       <c r="K13" s="15"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="O13" s="1"/>
       <c r="P13" s="16"/>
-      <c r="Q13" s="40"/>
+      <c r="Q13" s="54"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="26"/>
-      <c r="J14" s="40"/>
+      <c r="J14" s="54"/>
       <c r="K14" s="15"/>
       <c r="L14" s="1">
         <v>17</v>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="O14" s="1"/>
       <c r="P14" s="16"/>
-      <c r="Q14" s="40"/>
+      <c r="Q14" s="54"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="26"/>
-      <c r="J15" s="40"/>
+      <c r="J15" s="54"/>
       <c r="K15" s="15"/>
       <c r="L15" s="1">
         <v>10</v>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="O15" s="1"/>
       <c r="P15" s="16"/>
-      <c r="Q15" s="40"/>
+      <c r="Q15" s="54"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -1723,7 +1723,7 @@
         <f>B16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="40"/>
+      <c r="J16" s="54"/>
       <c r="K16" s="15"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -1736,7 +1736,7 @@
       <c r="P16" s="16">
         <v>16</v>
       </c>
-      <c r="Q16" s="40"/>
+      <c r="Q16" s="54"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -1761,7 +1761,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="26"/>
-      <c r="J17" s="40"/>
+      <c r="J17" s="54"/>
       <c r="K17" s="15">
         <v>8</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>10</v>
       </c>
       <c r="P17" s="16"/>
-      <c r="Q17" s="40"/>
+      <c r="Q17" s="54"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -1802,7 +1802,7 @@
         <f>B18</f>
         <v>0</v>
       </c>
-      <c r="J18" s="40"/>
+      <c r="J18" s="54"/>
       <c r="K18" s="15"/>
       <c r="L18" s="1">
         <v>5</v>
@@ -1817,7 +1817,7 @@
       <c r="P18" s="16">
         <v>8</v>
       </c>
-      <c r="Q18" s="40"/>
+      <c r="Q18" s="54"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
@@ -1839,7 +1839,7 @@
         <f>B19</f>
         <v>0</v>
       </c>
-      <c r="J19" s="40"/>
+      <c r="J19" s="54"/>
       <c r="K19" s="15"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -1850,7 +1850,7 @@
       <c r="P19" s="16">
         <v>16</v>
       </c>
-      <c r="Q19" s="40"/>
+      <c r="Q19" s="54"/>
     </row>
     <row r="20" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
@@ -1869,7 +1869,7 @@
         <f>B20</f>
         <v>0</v>
       </c>
-      <c r="J20" s="40"/>
+      <c r="J20" s="54"/>
       <c r="K20" s="15"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -1878,37 +1878,37 @@
       <c r="P20" s="16">
         <v>15</v>
       </c>
-      <c r="Q20" s="40"/>
+      <c r="Q20" s="54"/>
     </row>
     <row r="21" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="44"/>
-      <c r="B21" s="44"/>
-      <c r="C21" s="45"/>
+      <c r="A21" s="58"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="60"/>
       <c r="D21" s="30">
-        <f>((K7*D7)+(K8*D8)+(K9*D9)+(K10*D10)+(D11*K11)+(K12*D12)+(K13*D13)+(K14*D14)+(K15*D15)+(K16*D16)+(K17*D17)+(K18*D18)+(K19*D19)+(K20*D20))/K21</f>
+        <f t="shared" ref="D21:I21" si="1">((K7*D7)+(K8*D8)+(K9*D9)+(K10*D10)+(D11*K11)+(K12*D12)+(K13*D13)+(K14*D14)+(K15*D15)+(K16*D16)+(K17*D17)+(K18*D18)+(K19*D19)+(K20*D20))/K21</f>
         <v>0</v>
       </c>
       <c r="E21" s="30">
-        <f>((L7*E7)+(L8*E8)+(L9*E9)+(L10*E10)+(E11*L11)+(L12*E12)+(L13*E13)+(L14*E14)+(L15*E15)+(L16*E16)+(L17*E17)+(L18*E18)+(L19*E19)+(L20*E20))/L21</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F21" s="30">
-        <f>((M7*F7)+(M8*F8)+(M9*F9)+(M10*F10)+(F11*M11)+(M12*F12)+(M13*F13)+(M14*F14)+(M15*F15)+(M16*F16)+(M17*F17)+(M18*F18)+(M19*F19)+(M20*F20))/M21</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G21" s="30">
-        <f>((N7*G7)+(N8*G8)+(N9*G9)+(N10*G10)+(G11*N11)+(N12*G12)+(N13*G13)+(N14*G14)+(N15*G15)+(N16*G16)+(N17*G17)+(N18*G18)+(N19*G19)+(N20*G20))/N21</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H21" s="30">
-        <f>((O7*H7)+(O8*H8)+(O9*H9)+(O10*H10)+(H11*O11)+(O12*H12)+(O13*H13)+(O14*H14)+(O15*H15)+(O16*H16)+(O17*H17)+(O18*H18)+(O19*H19)+(O20*H20))/O21</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I21" s="30">
-        <f>((P7*I7)+(P8*I8)+(P9*I9)+(P10*I10)+(I11*P11)+(P12*I12)+(P13*I13)+(P14*I14)+(P15*I15)+(P16*I16)+(P17*I17)+(P18*I18)+(P19*I19)+(P20*I20))/P21</f>
-        <v>0</v>
-      </c>
-      <c r="J21" s="40"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="54"/>
       <c r="K21" s="17">
         <v>60</v>
       </c>
@@ -1927,7 +1927,7 @@
       <c r="P21" s="19">
         <v>60</v>
       </c>
-      <c r="Q21" s="40"/>
+      <c r="Q21" s="54"/>
     </row>
     <row r="22" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
@@ -1939,30 +1939,30 @@
       </c>
       <c r="C22" s="37"/>
       <c r="D22" s="7">
-        <f>((D21*K21)+(D5*K5))/K22</f>
+        <f t="shared" ref="D22:I22" si="2">((D21*K21)+(D5*K5))/K22</f>
         <v>0</v>
       </c>
       <c r="E22" s="7">
-        <f>((E21*L21)+(E5*L5))/L22</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F22" s="7">
-        <f>((F21*M21)+(F5*M5))/M22</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G22" s="7">
-        <f>((G21*N21)+(G5*N5))/N22</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H22" s="7">
-        <f>((H21*O21)+(H5*O5))/O22</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I22" s="30">
-        <f>((I21*P21)+(I5*P5))/P22</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="40"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="54"/>
       <c r="K22" s="3">
         <v>100</v>
       </c>
@@ -1981,89 +1981,89 @@
       <c r="P22" s="5">
         <v>100</v>
       </c>
-      <c r="Q22" s="40"/>
+      <c r="Q22" s="54"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="40"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="40"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="40"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="40"/>
-      <c r="K23" s="40"/>
-      <c r="L23" s="40"/>
-      <c r="M23" s="40"/>
-      <c r="N23" s="40"/>
-      <c r="O23" s="40"/>
-      <c r="P23" s="40"/>
-      <c r="Q23" s="40"/>
+      <c r="A23" s="54"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="54"/>
+      <c r="M23" s="54"/>
+      <c r="N23" s="54"/>
+      <c r="O23" s="54"/>
+      <c r="P23" s="54"/>
+      <c r="Q23" s="54"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="40"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="40"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="40"/>
-      <c r="K24" s="40"/>
-      <c r="L24" s="40"/>
-      <c r="M24" s="40"/>
-      <c r="N24" s="40"/>
-      <c r="O24" s="40"/>
-      <c r="P24" s="40"/>
-      <c r="Q24" s="40"/>
+      <c r="A24" s="54"/>
+      <c r="B24" s="54"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="54"/>
+      <c r="K24" s="54"/>
+      <c r="L24" s="54"/>
+      <c r="M24" s="54"/>
+      <c r="N24" s="54"/>
+      <c r="O24" s="54"/>
+      <c r="P24" s="54"/>
+      <c r="Q24" s="54"/>
     </row>
     <row r="25" spans="1:17" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A25" s="39" t="s">
+      <c r="A25" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="39"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="39"/>
-      <c r="K25" s="39"/>
-      <c r="L25" s="39"/>
-      <c r="M25" s="39"/>
-      <c r="N25" s="39"/>
-      <c r="O25" s="39"/>
-      <c r="P25" s="39"/>
-      <c r="Q25" s="40"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="53"/>
+      <c r="L25" s="53"/>
+      <c r="M25" s="53"/>
+      <c r="N25" s="53"/>
+      <c r="O25" s="53"/>
+      <c r="P25" s="53"/>
+      <c r="Q25" s="54"/>
     </row>
     <row r="26" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="50"/>
-      <c r="B26" s="50"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="40"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="40"/>
-      <c r="K26" s="40"/>
-      <c r="L26" s="40"/>
-      <c r="M26" s="40"/>
-      <c r="N26" s="40"/>
-      <c r="O26" s="40"/>
-      <c r="P26" s="40"/>
-      <c r="Q26" s="40"/>
+      <c r="A26" s="42"/>
+      <c r="B26" s="42"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="54"/>
+      <c r="K26" s="54"/>
+      <c r="L26" s="54"/>
+      <c r="M26" s="54"/>
+      <c r="N26" s="54"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="54"/>
+      <c r="Q26" s="54"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="50"/>
-      <c r="B27" s="50"/>
+      <c r="A27" s="42"/>
+      <c r="B27" s="42"/>
       <c r="D27" s="9" t="s">
         <v>0</v>
       </c>
@@ -2082,7 +2082,7 @@
       <c r="I27" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="J27" s="40"/>
+      <c r="J27" s="54"/>
       <c r="K27" s="9" t="s">
         <v>0</v>
       </c>
@@ -2101,39 +2101,39 @@
       <c r="P27" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="Q27" s="40"/>
+      <c r="Q27" s="54"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="50"/>
+      <c r="A28" s="42"/>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="51"/>
+      <c r="C28" s="43"/>
       <c r="D28" s="25">
         <f>C28</f>
         <v>0</v>
       </c>
-      <c r="E28" s="48">
+      <c r="E28" s="40">
         <f>C28</f>
         <v>0</v>
       </c>
-      <c r="F28" s="48">
+      <c r="F28" s="40">
         <f>C28</f>
         <v>0</v>
       </c>
-      <c r="G28" s="48">
+      <c r="G28" s="40">
         <f>C28</f>
         <v>0</v>
       </c>
-      <c r="H28" s="48">
+      <c r="H28" s="40">
         <f>C28</f>
         <v>0</v>
       </c>
-      <c r="I28" s="49">
+      <c r="I28" s="41">
         <f>C28</f>
         <v>0</v>
       </c>
-      <c r="J28" s="40"/>
+      <c r="J28" s="54"/>
       <c r="K28" s="12">
         <v>15</v>
       </c>
@@ -2152,14 +2152,14 @@
       <c r="P28" s="14">
         <v>15</v>
       </c>
-      <c r="Q28" s="40"/>
+      <c r="Q28" s="54"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="50"/>
+      <c r="A29" s="42"/>
       <c r="B29" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C29" s="51"/>
+      <c r="C29" s="43"/>
       <c r="D29" s="23">
         <f>C29</f>
         <v>0</v>
@@ -2180,11 +2180,11 @@
         <f>C29</f>
         <v>0</v>
       </c>
-      <c r="I29" s="54">
+      <c r="I29" s="46">
         <f>C29</f>
         <v>0</v>
       </c>
-      <c r="J29" s="40"/>
+      <c r="J29" s="54"/>
       <c r="K29" s="15">
         <v>5</v>
       </c>
@@ -2203,39 +2203,39 @@
       <c r="P29" s="16">
         <v>5</v>
       </c>
-      <c r="Q29" s="40"/>
+      <c r="Q29" s="54"/>
     </row>
     <row r="30" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="50"/>
+      <c r="A30" s="42"/>
       <c r="B30" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C30" s="51"/>
-      <c r="D30" s="58">
+      <c r="C30" s="43"/>
+      <c r="D30" s="50">
         <f>C30</f>
         <v>0</v>
       </c>
-      <c r="E30" s="59">
+      <c r="E30" s="51">
         <f>C30</f>
         <v>0</v>
       </c>
-      <c r="F30" s="59">
+      <c r="F30" s="51">
         <f>C30</f>
         <v>0</v>
       </c>
-      <c r="G30" s="59">
+      <c r="G30" s="51">
         <f>C30</f>
         <v>0</v>
       </c>
-      <c r="H30" s="59">
+      <c r="H30" s="51">
         <f>C30</f>
         <v>0</v>
       </c>
-      <c r="I30" s="60">
+      <c r="I30" s="52">
         <f>C30</f>
         <v>0</v>
       </c>
-      <c r="J30" s="40"/>
+      <c r="J30" s="54"/>
       <c r="K30" s="17">
         <v>40</v>
       </c>
@@ -2254,56 +2254,56 @@
       <c r="P30" s="19">
         <v>40</v>
       </c>
-      <c r="Q30" s="40"/>
+      <c r="Q30" s="54"/>
     </row>
     <row r="31" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="36"/>
       <c r="B31" s="36"/>
       <c r="C31" s="37"/>
-      <c r="D31" s="52">
+      <c r="D31" s="44">
         <f>(D28*K28+D29*K29+D30*K30)/K31</f>
         <v>0</v>
       </c>
-      <c r="E31" s="52">
+      <c r="E31" s="44">
         <f>(E28*L28+E29*L29+E30*L30)/L31</f>
         <v>0</v>
       </c>
-      <c r="F31" s="52">
+      <c r="F31" s="44">
         <f>(F28*M28+F29*M29+F30*M30)/M31</f>
         <v>0</v>
       </c>
-      <c r="G31" s="52">
-        <f t="shared" ref="E31:I31" si="1">(G28*N28+G29*N29+G30*N30)/N31</f>
-        <v>0</v>
-      </c>
-      <c r="H31" s="52">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I31" s="52">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J31" s="40"/>
-      <c r="K31" s="55">
+      <c r="G31" s="44">
+        <f t="shared" ref="G31:I31" si="3">(G28*N28+G29*N29+G30*N30)/N31</f>
+        <v>0</v>
+      </c>
+      <c r="H31" s="44">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I31" s="44">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="54"/>
+      <c r="K31" s="47">
         <v>60</v>
       </c>
-      <c r="L31" s="56">
+      <c r="L31" s="48">
         <v>60</v>
       </c>
-      <c r="M31" s="56">
+      <c r="M31" s="48">
         <v>60</v>
       </c>
-      <c r="N31" s="56">
+      <c r="N31" s="48">
         <v>60</v>
       </c>
-      <c r="O31" s="56">
+      <c r="O31" s="48">
         <v>60</v>
       </c>
-      <c r="P31" s="57">
+      <c r="P31" s="49">
         <v>60</v>
       </c>
-      <c r="Q31" s="40"/>
+      <c r="Q31" s="54"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
@@ -2312,21 +2312,21 @@
       <c r="B32" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C32" s="43"/>
-      <c r="D32" s="40"/>
-      <c r="E32" s="40"/>
-      <c r="F32" s="40"/>
-      <c r="G32" s="40"/>
-      <c r="H32" s="40"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="40"/>
-      <c r="K32" s="42"/>
-      <c r="L32" s="42"/>
-      <c r="M32" s="42"/>
-      <c r="N32" s="42"/>
-      <c r="O32" s="42"/>
-      <c r="P32" s="42"/>
-      <c r="Q32" s="40"/>
+      <c r="C32" s="57"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="54"/>
+      <c r="I32" s="54"/>
+      <c r="J32" s="54"/>
+      <c r="K32" s="56"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="56"/>
+      <c r="N32" s="56"/>
+      <c r="O32" s="56"/>
+      <c r="P32" s="56"/>
+      <c r="Q32" s="54"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
@@ -2351,7 +2351,7 @@
         <f>$B33</f>
         <v>0</v>
       </c>
-      <c r="J33" s="40"/>
+      <c r="J33" s="54"/>
       <c r="K33" s="12">
         <v>16</v>
       </c>
@@ -2364,7 +2364,7 @@
       <c r="P33" s="14">
         <v>4</v>
       </c>
-      <c r="Q33" s="40"/>
+      <c r="Q33" s="54"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
@@ -2386,7 +2386,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="26"/>
-      <c r="J34" s="40"/>
+      <c r="J34" s="54"/>
       <c r="K34" s="15">
         <v>8</v>
       </c>
@@ -2397,7 +2397,7 @@
         <v>10</v>
       </c>
       <c r="P34" s="16"/>
-      <c r="Q34" s="40"/>
+      <c r="Q34" s="54"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="26"/>
-      <c r="J35" s="40"/>
+      <c r="J35" s="54"/>
       <c r="K35" s="15"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="O35" s="1"/>
       <c r="P35" s="16"/>
-      <c r="Q35" s="40"/>
+      <c r="Q35" s="54"/>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
@@ -2444,7 +2444,7 @@
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
       <c r="I36" s="26"/>
-      <c r="J36" s="40"/>
+      <c r="J36" s="54"/>
       <c r="K36" s="15"/>
       <c r="L36" s="1">
         <v>12</v>
@@ -2453,7 +2453,7 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
       <c r="P36" s="16"/>
-      <c r="Q36" s="40"/>
+      <c r="Q36" s="54"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
@@ -2475,7 +2475,7 @@
         <f>$B37</f>
         <v>0</v>
       </c>
-      <c r="J37" s="40"/>
+      <c r="J37" s="54"/>
       <c r="K37" s="15"/>
       <c r="L37" s="1">
         <v>4</v>
@@ -2486,7 +2486,7 @@
       <c r="P37" s="16">
         <v>13</v>
       </c>
-      <c r="Q37" s="40"/>
+      <c r="Q37" s="54"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
@@ -2508,7 +2508,7 @@
         <f>B38</f>
         <v>0</v>
       </c>
-      <c r="J38" s="40"/>
+      <c r="J38" s="54"/>
       <c r="K38" s="15"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -2519,7 +2519,7 @@
       <c r="P38" s="16">
         <v>13</v>
       </c>
-      <c r="Q38" s="40"/>
+      <c r="Q38" s="54"/>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
@@ -2538,7 +2538,7 @@
         <f>$B39</f>
         <v>0</v>
       </c>
-      <c r="J39" s="40"/>
+      <c r="J39" s="54"/>
       <c r="K39" s="15"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -2547,7 +2547,7 @@
       <c r="P39" s="16">
         <v>10</v>
       </c>
-      <c r="Q39" s="40"/>
+      <c r="Q39" s="54"/>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
@@ -2566,7 +2566,7 @@
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
       <c r="I40" s="26"/>
-      <c r="J40" s="40"/>
+      <c r="J40" s="54"/>
       <c r="K40" s="15"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1">
@@ -2575,7 +2575,7 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
       <c r="P40" s="16"/>
-      <c r="Q40" s="40"/>
+      <c r="Q40" s="54"/>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
@@ -2597,7 +2597,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="26"/>
-      <c r="J41" s="40"/>
+      <c r="J41" s="54"/>
       <c r="K41" s="15"/>
       <c r="L41" s="1">
         <v>4</v>
@@ -2608,7 +2608,7 @@
         <v>22</v>
       </c>
       <c r="P41" s="16"/>
-      <c r="Q41" s="40"/>
+      <c r="Q41" s="54"/>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
@@ -2636,7 +2636,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="26"/>
-      <c r="J42" s="40"/>
+      <c r="J42" s="54"/>
       <c r="K42" s="15">
         <v>8</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>4</v>
       </c>
       <c r="P42" s="16"/>
-      <c r="Q42" s="40"/>
+      <c r="Q42" s="54"/>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
@@ -2679,7 +2679,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="26"/>
-      <c r="J43" s="40"/>
+      <c r="J43" s="54"/>
       <c r="K43" s="15">
         <v>8</v>
       </c>
@@ -2694,7 +2694,7 @@
         <v>4</v>
       </c>
       <c r="P43" s="16"/>
-      <c r="Q43" s="40"/>
+      <c r="Q43" s="54"/>
     </row>
     <row r="44" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
@@ -2713,7 +2713,7 @@
       <c r="G44" s="34"/>
       <c r="H44" s="34"/>
       <c r="I44" s="35"/>
-      <c r="J44" s="40"/>
+      <c r="J44" s="54"/>
       <c r="K44" s="15"/>
       <c r="L44" s="1">
         <v>12</v>
@@ -2722,37 +2722,37 @@
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="16"/>
-      <c r="Q44" s="40"/>
+      <c r="Q44" s="54"/>
     </row>
     <row r="45" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="44"/>
-      <c r="B45" s="44"/>
-      <c r="C45" s="44"/>
+      <c r="A45" s="58"/>
+      <c r="B45" s="58"/>
+      <c r="C45" s="58"/>
       <c r="D45" s="30">
-        <f>((K33*D33)+(K34*D34)+(D35*K35)+(K36*D36)+(K37*D37)+(K38*D38)+(K39*D39)+(K40*D40)+(K41*D41)+(K42*D42)+(K43*D43)+(K44*D44))/K45</f>
+        <f t="shared" ref="D45:I45" si="4">((K33*D33)+(K34*D34)+(D35*K35)+(K36*D36)+(K37*D37)+(K38*D38)+(K39*D39)+(K40*D40)+(K41*D41)+(K42*D42)+(K43*D43)+(K44*D44))/K45</f>
         <v>0</v>
       </c>
       <c r="E45" s="30">
-        <f>((L33*E33)+(L34*E34)+(E35*L35)+(L36*E36)+(L37*E37)+(L38*E38)+(L39*E39)+(L40*E40)+(L41*E41)+(L42*E42)+(L43*E43)+(L44*E44))/L45</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F45" s="30">
-        <f>((M33*F33)+(M34*F34)+(F35*M35)+(M36*F36)+(M37*F37)+(M38*F38)+(M39*F39)+(M40*F40)+(M41*F41)+(M42*F42)+(M43*F43)+(M44*F44))/M45</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G45" s="30">
-        <f>((N33*G33)+(N34*G34)+(G35*N35)+(N36*G36)+(N37*G37)+(N38*G38)+(N39*G39)+(N40*G40)+(N41*G41)+(N42*G42)+(N43*G43)+(N44*G44))/N45</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H45" s="30">
-        <f>((O33*H33)+(O34*H34)+(H35*O35)+(O36*H36)+(O37*H37)+(O38*H38)+(O39*H39)+(O40*H40)+(O41*H41)+(O42*H42)+(O43*H43)+(O44*H44))/O45</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I45" s="30">
-        <f>((P33*I33)+(P34*I34)+(I35*P35)+(P36*I36)+(P37*I37)+(P38*I38)+(P39*I39)+(P40*I40)+(P41*I41)+(P42*I42)+(P43*I43)+(P44*I44))/P45</f>
-        <v>0</v>
-      </c>
-      <c r="J45" s="40"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="54"/>
       <c r="K45" s="17">
         <v>40</v>
       </c>
@@ -2771,7 +2771,7 @@
       <c r="P45" s="19">
         <v>40</v>
       </c>
-      <c r="Q45" s="40"/>
+      <c r="Q45" s="54"/>
     </row>
     <row r="46" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
@@ -2782,31 +2782,31 @@
         <v>0</v>
       </c>
       <c r="C46" s="37"/>
-      <c r="D46" s="52">
-        <f>((D45*K45)+(D31*K31))/K46</f>
-        <v>0</v>
-      </c>
-      <c r="E46" s="52">
-        <f>((E45*L45)+(E31*L31))/L46</f>
-        <v>0</v>
-      </c>
-      <c r="F46" s="52">
-        <f>((F45*M45)+(F31*M31))/M46</f>
-        <v>0</v>
-      </c>
-      <c r="G46" s="52">
-        <f>((G45*N45)+(G31*N31))/N46</f>
-        <v>0</v>
-      </c>
-      <c r="H46" s="52">
-        <f>((H45*O45)+(H31*O31))/O46</f>
-        <v>0</v>
-      </c>
-      <c r="I46" s="53">
-        <f>((I45*P45)+(I31*P31))/P46</f>
-        <v>0</v>
-      </c>
-      <c r="J46" s="40"/>
+      <c r="D46" s="44">
+        <f t="shared" ref="D46:I46" si="5">((D45*K45)+(D31*K31))/K46</f>
+        <v>0</v>
+      </c>
+      <c r="E46" s="44">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F46" s="44">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G46" s="44">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="44">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I46" s="45">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="54"/>
       <c r="K46" s="3">
         <v>100</v>
       </c>
@@ -2825,128 +2825,128 @@
       <c r="P46" s="5">
         <v>100</v>
       </c>
-      <c r="Q46" s="40"/>
+      <c r="Q46" s="54"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" s="40"/>
-      <c r="B47" s="40"/>
-      <c r="C47" s="40"/>
-      <c r="D47" s="40"/>
-      <c r="E47" s="40"/>
-      <c r="F47" s="40"/>
-      <c r="G47" s="40"/>
-      <c r="H47" s="40"/>
-      <c r="I47" s="40"/>
-      <c r="J47" s="40"/>
-      <c r="K47" s="40"/>
-      <c r="L47" s="40"/>
-      <c r="M47" s="40"/>
-      <c r="N47" s="40"/>
-      <c r="O47" s="40"/>
-      <c r="P47" s="40"/>
-      <c r="Q47" s="40"/>
+      <c r="A47" s="54"/>
+      <c r="B47" s="54"/>
+      <c r="C47" s="54"/>
+      <c r="D47" s="54"/>
+      <c r="E47" s="54"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="54"/>
+      <c r="I47" s="54"/>
+      <c r="J47" s="54"/>
+      <c r="K47" s="54"/>
+      <c r="L47" s="54"/>
+      <c r="M47" s="54"/>
+      <c r="N47" s="54"/>
+      <c r="O47" s="54"/>
+      <c r="P47" s="54"/>
+      <c r="Q47" s="54"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="40"/>
-      <c r="B48" s="40"/>
-      <c r="C48" s="40"/>
-      <c r="D48" s="40"/>
-      <c r="E48" s="40"/>
-      <c r="F48" s="40"/>
-      <c r="G48" s="40"/>
-      <c r="H48" s="40"/>
-      <c r="I48" s="40"/>
-      <c r="J48" s="40"/>
-      <c r="K48" s="40"/>
-      <c r="L48" s="40"/>
-      <c r="M48" s="40"/>
-      <c r="N48" s="40"/>
-      <c r="O48" s="40"/>
-      <c r="P48" s="40"/>
-      <c r="Q48" s="40"/>
+      <c r="A48" s="54"/>
+      <c r="B48" s="54"/>
+      <c r="C48" s="54"/>
+      <c r="D48" s="54"/>
+      <c r="E48" s="54"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="54"/>
+      <c r="J48" s="54"/>
+      <c r="K48" s="54"/>
+      <c r="L48" s="54"/>
+      <c r="M48" s="54"/>
+      <c r="N48" s="54"/>
+      <c r="O48" s="54"/>
+      <c r="P48" s="54"/>
+      <c r="Q48" s="54"/>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="40"/>
-      <c r="B49" s="40"/>
-      <c r="C49" s="40"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="40"/>
-      <c r="F49" s="40"/>
-      <c r="G49" s="40"/>
-      <c r="H49" s="40"/>
-      <c r="I49" s="40"/>
-      <c r="J49" s="40"/>
-      <c r="K49" s="40"/>
-      <c r="L49" s="40"/>
-      <c r="M49" s="40"/>
-      <c r="N49" s="40"/>
-      <c r="O49" s="40"/>
-      <c r="P49" s="40"/>
-      <c r="Q49" s="40"/>
+      <c r="A49" s="54"/>
+      <c r="B49" s="54"/>
+      <c r="C49" s="54"/>
+      <c r="D49" s="54"/>
+      <c r="E49" s="54"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="54"/>
+      <c r="I49" s="54"/>
+      <c r="J49" s="54"/>
+      <c r="K49" s="54"/>
+      <c r="L49" s="54"/>
+      <c r="M49" s="54"/>
+      <c r="N49" s="54"/>
+      <c r="O49" s="54"/>
+      <c r="P49" s="54"/>
+      <c r="Q49" s="54"/>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A50" s="40"/>
-      <c r="B50" s="40"/>
-      <c r="C50" s="40"/>
-      <c r="D50" s="40"/>
-      <c r="E50" s="40"/>
-      <c r="F50" s="40"/>
-      <c r="G50" s="40"/>
-      <c r="H50" s="40"/>
-      <c r="I50" s="40"/>
-      <c r="J50" s="40"/>
-      <c r="K50" s="40"/>
-      <c r="L50" s="40"/>
-      <c r="M50" s="40"/>
-      <c r="N50" s="40"/>
-      <c r="O50" s="40"/>
-      <c r="P50" s="40"/>
-      <c r="Q50" s="40"/>
+      <c r="A50" s="54"/>
+      <c r="B50" s="54"/>
+      <c r="C50" s="54"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="54"/>
+      <c r="I50" s="54"/>
+      <c r="J50" s="54"/>
+      <c r="K50" s="54"/>
+      <c r="L50" s="54"/>
+      <c r="M50" s="54"/>
+      <c r="N50" s="54"/>
+      <c r="O50" s="54"/>
+      <c r="P50" s="54"/>
+      <c r="Q50" s="54"/>
     </row>
     <row r="51" spans="1:17" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A51" s="39" t="s">
+      <c r="A51" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="B51" s="39"/>
-      <c r="C51" s="39"/>
-      <c r="D51" s="39"/>
-      <c r="E51" s="39"/>
-      <c r="F51" s="39"/>
-      <c r="G51" s="39"/>
-      <c r="H51" s="39"/>
-      <c r="I51" s="39"/>
-      <c r="J51" s="39"/>
-      <c r="K51" s="39"/>
-      <c r="L51" s="39"/>
-      <c r="M51" s="39"/>
-      <c r="N51" s="39"/>
-      <c r="O51" s="39"/>
-      <c r="P51" s="39"/>
-      <c r="Q51" s="40"/>
+      <c r="B51" s="53"/>
+      <c r="C51" s="53"/>
+      <c r="D51" s="53"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="53"/>
+      <c r="G51" s="53"/>
+      <c r="H51" s="53"/>
+      <c r="I51" s="53"/>
+      <c r="J51" s="53"/>
+      <c r="K51" s="53"/>
+      <c r="L51" s="53"/>
+      <c r="M51" s="53"/>
+      <c r="N51" s="53"/>
+      <c r="O51" s="53"/>
+      <c r="P51" s="53"/>
+      <c r="Q51" s="54"/>
     </row>
     <row r="52" spans="1:17" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="46"/>
-      <c r="B52" s="46"/>
-      <c r="C52" s="46"/>
-      <c r="D52" s="46"/>
-      <c r="E52" s="46"/>
-      <c r="F52" s="46"/>
-      <c r="G52" s="46"/>
-      <c r="H52" s="46"/>
-      <c r="I52" s="46"/>
-      <c r="J52" s="46"/>
-      <c r="K52" s="46"/>
-      <c r="L52" s="46"/>
-      <c r="M52" s="46"/>
-      <c r="N52" s="46"/>
-      <c r="O52" s="46"/>
-      <c r="P52" s="46"/>
-      <c r="Q52" s="40"/>
+      <c r="A52" s="59"/>
+      <c r="B52" s="59"/>
+      <c r="C52" s="59"/>
+      <c r="D52" s="59"/>
+      <c r="E52" s="59"/>
+      <c r="F52" s="59"/>
+      <c r="G52" s="59"/>
+      <c r="H52" s="59"/>
+      <c r="I52" s="59"/>
+      <c r="J52" s="59"/>
+      <c r="K52" s="59"/>
+      <c r="L52" s="59"/>
+      <c r="M52" s="59"/>
+      <c r="N52" s="59"/>
+      <c r="O52" s="59"/>
+      <c r="P52" s="59"/>
+      <c r="Q52" s="54"/>
     </row>
     <row r="53" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="40"/>
-      <c r="B53" s="40"/>
-      <c r="C53" s="40"/>
+      <c r="A53" s="54"/>
+      <c r="B53" s="54"/>
+      <c r="C53" s="54"/>
       <c r="D53" s="3" t="s">
         <v>0</v>
       </c>
@@ -2965,89 +2965,89 @@
       <c r="I53" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J53" s="40"/>
-      <c r="K53" s="40"/>
-      <c r="L53" s="40"/>
-      <c r="M53" s="40"/>
-      <c r="N53" s="40"/>
-      <c r="O53" s="40"/>
-      <c r="P53" s="40"/>
-      <c r="Q53" s="40"/>
+      <c r="J53" s="54"/>
+      <c r="K53" s="54"/>
+      <c r="L53" s="54"/>
+      <c r="M53" s="54"/>
+      <c r="N53" s="54"/>
+      <c r="O53" s="54"/>
+      <c r="P53" s="54"/>
+      <c r="Q53" s="54"/>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A54" s="40"/>
-      <c r="B54" s="40"/>
-      <c r="C54" s="40"/>
+      <c r="A54" s="54"/>
+      <c r="B54" s="54"/>
+      <c r="C54" s="54"/>
       <c r="D54" s="1">
-        <f>(D46+D22)/2</f>
+        <f t="shared" ref="D54:I54" si="6">(D46+D22)/2</f>
         <v>0</v>
       </c>
       <c r="E54" s="1">
-        <f>(E46+E22)/2</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F54" s="1">
-        <f>(F46+F22)/2</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G54" s="1">
-        <f>(G46+G22)/2</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H54" s="1">
-        <f>(H46+H22)/2</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I54" s="1">
-        <f>(I46+I22)/2</f>
-        <v>0</v>
-      </c>
-      <c r="J54" s="40"/>
-      <c r="K54" s="40"/>
-      <c r="L54" s="40"/>
-      <c r="M54" s="40"/>
-      <c r="N54" s="40"/>
-      <c r="O54" s="40"/>
-      <c r="P54" s="40"/>
-      <c r="Q54" s="40"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="54"/>
+      <c r="K54" s="54"/>
+      <c r="L54" s="54"/>
+      <c r="M54" s="54"/>
+      <c r="N54" s="54"/>
+      <c r="O54" s="54"/>
+      <c r="P54" s="54"/>
+      <c r="Q54" s="54"/>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A55" s="40"/>
-      <c r="B55" s="40"/>
-      <c r="C55" s="40"/>
-      <c r="D55" s="40"/>
-      <c r="E55" s="40"/>
-      <c r="F55" s="40"/>
-      <c r="G55" s="40"/>
-      <c r="H55" s="40"/>
-      <c r="I55" s="40"/>
-      <c r="J55" s="40"/>
-      <c r="K55" s="40"/>
-      <c r="L55" s="40"/>
-      <c r="M55" s="40"/>
-      <c r="N55" s="40"/>
-      <c r="O55" s="40"/>
-      <c r="P55" s="40"/>
-      <c r="Q55" s="40"/>
+      <c r="A55" s="54"/>
+      <c r="B55" s="54"/>
+      <c r="C55" s="54"/>
+      <c r="D55" s="54"/>
+      <c r="E55" s="54"/>
+      <c r="F55" s="54"/>
+      <c r="G55" s="54"/>
+      <c r="H55" s="54"/>
+      <c r="I55" s="54"/>
+      <c r="J55" s="54"/>
+      <c r="K55" s="54"/>
+      <c r="L55" s="54"/>
+      <c r="M55" s="54"/>
+      <c r="N55" s="54"/>
+      <c r="O55" s="54"/>
+      <c r="P55" s="54"/>
+      <c r="Q55" s="54"/>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A56" s="40"/>
-      <c r="B56" s="40"/>
-      <c r="C56" s="40"/>
-      <c r="D56" s="40"/>
-      <c r="E56" s="40"/>
-      <c r="F56" s="40"/>
-      <c r="G56" s="40"/>
-      <c r="H56" s="40"/>
-      <c r="I56" s="40"/>
-      <c r="J56" s="40"/>
-      <c r="K56" s="40"/>
-      <c r="L56" s="40"/>
-      <c r="M56" s="40"/>
-      <c r="N56" s="40"/>
-      <c r="O56" s="40"/>
-      <c r="P56" s="40"/>
-      <c r="Q56" s="40"/>
+      <c r="A56" s="54"/>
+      <c r="B56" s="54"/>
+      <c r="C56" s="54"/>
+      <c r="D56" s="54"/>
+      <c r="E56" s="54"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="54"/>
+      <c r="H56" s="54"/>
+      <c r="I56" s="54"/>
+      <c r="J56" s="54"/>
+      <c r="K56" s="54"/>
+      <c r="L56" s="54"/>
+      <c r="M56" s="54"/>
+      <c r="N56" s="54"/>
+      <c r="O56" s="54"/>
+      <c r="P56" s="54"/>
+      <c r="Q56" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="21">
@@ -3077,7 +3077,7 @@
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="8"/>
-        <cfvo type="num" val="12"/>
+        <cfvo type="num" val="11"/>
         <color rgb="FFFF0000"/>
         <color rgb="FF92D050"/>
       </colorScale>
@@ -3087,7 +3087,7 @@
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="8"/>
-        <cfvo type="num" val="12"/>
+        <cfvo type="num" val="11"/>
         <color rgb="FFFF0000"/>
         <color rgb="FF92D050"/>
       </colorScale>

--- a/BUT2/1-DOC/SemestreBUT2_RA_complete.xlsx
+++ b/BUT2/1-DOC/SemestreBUT2_RA_complete.xlsx
@@ -14,25 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="71">
-  <si>
-    <t>UE1.1</t>
-  </si>
-  <si>
-    <t>UE1.2</t>
-  </si>
-  <si>
-    <t>UE1.3</t>
-  </si>
-  <si>
-    <t>UE1.4</t>
-  </si>
-  <si>
-    <t>UE1.5</t>
-  </si>
-  <si>
-    <t>UE1.6</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="77">
   <si>
     <t>à remplir</t>
   </si>
@@ -227,6 +209,42 @@
   </si>
   <si>
     <t>Virtualisation</t>
+  </si>
+  <si>
+    <t>UE1</t>
+  </si>
+  <si>
+    <t>UE2</t>
+  </si>
+  <si>
+    <t>UE3</t>
+  </si>
+  <si>
+    <t>UE4</t>
+  </si>
+  <si>
+    <t>UE5</t>
+  </si>
+  <si>
+    <t>UE6</t>
+  </si>
+  <si>
+    <t>UE4.1</t>
+  </si>
+  <si>
+    <t>UE4.2</t>
+  </si>
+  <si>
+    <t>UE4.3</t>
+  </si>
+  <si>
+    <t>UE4.4</t>
+  </si>
+  <si>
+    <t>UE4.5</t>
+  </si>
+  <si>
+    <t>UE4.6</t>
   </si>
 </sst>
 </file>
@@ -854,28 +872,28 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1192,93 +1210,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="54"/>
+      <c r="A1" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="59"/>
+      <c r="P1" s="59"/>
+      <c r="Q1" s="53"/>
     </row>
     <row r="2" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="54"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="54"/>
-      <c r="P2" s="54"/>
-      <c r="Q2" s="54"/>
+      <c r="A2" s="53"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+      <c r="Q2" s="53"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="54"/>
-      <c r="B3" s="54"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="53"/>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="J3" s="54"/>
+        <v>57</v>
+      </c>
+      <c r="J3" s="53"/>
       <c r="K3" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q3" s="54"/>
+        <v>57</v>
+      </c>
+      <c r="Q3" s="53"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="54"/>
-      <c r="B4" s="54"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="53"/>
       <c r="C4" s="32"/>
       <c r="D4" s="39">
         <f>C4</f>
@@ -1304,21 +1322,21 @@
         <f>C4</f>
         <v>0</v>
       </c>
-      <c r="J4" s="54"/>
+      <c r="J4" s="53"/>
       <c r="K4" s="12"/>
       <c r="L4" s="13"/>
       <c r="M4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
       <c r="P4" s="14"/>
-      <c r="Q4" s="54"/>
+      <c r="Q4" s="53"/>
       <c r="S4" s="31" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="55"/>
-      <c r="B5" s="55"/>
+      <c r="A5" s="60"/>
+      <c r="B5" s="60"/>
       <c r="C5" s="37"/>
       <c r="D5" s="20">
         <f>(D4*K5)/K5</f>
@@ -1344,7 +1362,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J5" s="54"/>
+      <c r="J5" s="53"/>
       <c r="K5" s="17">
         <v>40</v>
       </c>
@@ -1363,38 +1381,38 @@
       <c r="P5" s="19">
         <v>40</v>
       </c>
-      <c r="Q5" s="54"/>
+      <c r="Q5" s="53"/>
     </row>
     <row r="6" spans="1:19" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C6" s="57"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="56"/>
-      <c r="M6" s="56"/>
-      <c r="N6" s="56"/>
-      <c r="O6" s="56"/>
-      <c r="P6" s="56"/>
-      <c r="Q6" s="54"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="58"/>
+      <c r="L6" s="58"/>
+      <c r="M6" s="58"/>
+      <c r="N6" s="58"/>
+      <c r="O6" s="58"/>
+      <c r="P6" s="58"/>
+      <c r="Q6" s="53"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B7" s="32"/>
       <c r="C7" s="8" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D7" s="25">
         <f>B7</f>
@@ -1414,7 +1432,7 @@
       </c>
       <c r="H7" s="27"/>
       <c r="I7" s="28"/>
-      <c r="J7" s="54"/>
+      <c r="J7" s="53"/>
       <c r="K7" s="12">
         <v>15</v>
       </c>
@@ -1429,15 +1447,15 @@
       </c>
       <c r="O7" s="13"/>
       <c r="P7" s="14"/>
-      <c r="Q7" s="54"/>
+      <c r="Q7" s="53"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B8" s="32"/>
       <c r="C8" s="8" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D8" s="23">
         <f>B8</f>
@@ -1451,7 +1469,7 @@
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="26"/>
-      <c r="J8" s="54"/>
+      <c r="J8" s="53"/>
       <c r="K8" s="15">
         <v>10</v>
       </c>
@@ -1462,15 +1480,15 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="16"/>
-      <c r="Q8" s="54"/>
+      <c r="Q8" s="53"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B9" s="32"/>
       <c r="C9" s="8" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D9" s="23">
         <f>B9</f>
@@ -1487,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="26"/>
-      <c r="J9" s="54"/>
+      <c r="J9" s="53"/>
       <c r="K9" s="15">
         <v>12</v>
       </c>
@@ -1500,15 +1518,15 @@
         <v>10</v>
       </c>
       <c r="P9" s="16"/>
-      <c r="Q9" s="54"/>
+      <c r="Q9" s="53"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B10" s="32"/>
       <c r="C10" s="8" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D10" s="29">
         <f>B10</f>
@@ -1525,7 +1543,7 @@
         <f>B10</f>
         <v>0</v>
       </c>
-      <c r="J10" s="54"/>
+      <c r="J10" s="53"/>
       <c r="K10" s="15">
         <v>15</v>
       </c>
@@ -1538,15 +1556,15 @@
       <c r="P10" s="16">
         <v>5</v>
       </c>
-      <c r="Q10" s="54"/>
+      <c r="Q10" s="53"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B11" s="32"/>
       <c r="C11" s="8" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D11" s="29"/>
       <c r="E11" s="6"/>
@@ -1557,7 +1575,7 @@
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
       <c r="I11" s="26"/>
-      <c r="J11" s="54"/>
+      <c r="J11" s="53"/>
       <c r="K11" s="15"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1">
@@ -1566,15 +1584,15 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="16"/>
-      <c r="Q11" s="54"/>
+      <c r="Q11" s="53"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B12" s="32"/>
       <c r="C12" s="8" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D12" s="29"/>
       <c r="E12" s="38">
@@ -1588,7 +1606,7 @@
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="26"/>
-      <c r="J12" s="54"/>
+      <c r="J12" s="53"/>
       <c r="K12" s="15"/>
       <c r="L12" s="1">
         <v>5</v>
@@ -1599,15 +1617,15 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="16"/>
-      <c r="Q12" s="54"/>
+      <c r="Q12" s="53"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B13" s="32"/>
       <c r="C13" s="8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D13" s="29"/>
       <c r="E13" s="6"/>
@@ -1618,7 +1636,7 @@
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="26"/>
-      <c r="J13" s="54"/>
+      <c r="J13" s="53"/>
       <c r="K13" s="15"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -1627,15 +1645,15 @@
       </c>
       <c r="O13" s="1"/>
       <c r="P13" s="16"/>
-      <c r="Q13" s="54"/>
+      <c r="Q13" s="53"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B14" s="32"/>
       <c r="C14" s="8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D14" s="29"/>
       <c r="E14" s="6">
@@ -1649,7 +1667,7 @@
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="26"/>
-      <c r="J14" s="54"/>
+      <c r="J14" s="53"/>
       <c r="K14" s="15"/>
       <c r="L14" s="1">
         <v>17</v>
@@ -1660,15 +1678,15 @@
       </c>
       <c r="O14" s="1"/>
       <c r="P14" s="16"/>
-      <c r="Q14" s="54"/>
+      <c r="Q14" s="53"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B15" s="32"/>
       <c r="C15" s="8" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D15" s="29"/>
       <c r="E15" s="6">
@@ -1685,7 +1703,7 @@
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="26"/>
-      <c r="J15" s="54"/>
+      <c r="J15" s="53"/>
       <c r="K15" s="15"/>
       <c r="L15" s="1">
         <v>10</v>
@@ -1698,15 +1716,15 @@
       </c>
       <c r="O15" s="1"/>
       <c r="P15" s="16"/>
-      <c r="Q15" s="54"/>
+      <c r="Q15" s="53"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B16" s="32"/>
       <c r="C16" s="8" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D16" s="29"/>
       <c r="E16" s="6"/>
@@ -1723,7 +1741,7 @@
         <f>B16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="54"/>
+      <c r="J16" s="53"/>
       <c r="K16" s="15"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -1736,15 +1754,15 @@
       <c r="P16" s="16">
         <v>16</v>
       </c>
-      <c r="Q16" s="54"/>
+      <c r="Q16" s="53"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B17" s="32"/>
       <c r="C17" s="8" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D17" s="23">
         <f>B17</f>
@@ -1761,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="26"/>
-      <c r="J17" s="54"/>
+      <c r="J17" s="53"/>
       <c r="K17" s="15">
         <v>8</v>
       </c>
@@ -1774,15 +1792,15 @@
         <v>10</v>
       </c>
       <c r="P17" s="16"/>
-      <c r="Q17" s="54"/>
+      <c r="Q17" s="53"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B18" s="32"/>
       <c r="C18" s="8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D18" s="23"/>
       <c r="E18" s="6">
@@ -1802,7 +1820,7 @@
         <f>B18</f>
         <v>0</v>
       </c>
-      <c r="J18" s="54"/>
+      <c r="J18" s="53"/>
       <c r="K18" s="15"/>
       <c r="L18" s="1">
         <v>5</v>
@@ -1817,15 +1835,15 @@
       <c r="P18" s="16">
         <v>8</v>
       </c>
-      <c r="Q18" s="54"/>
+      <c r="Q18" s="53"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B19" s="32"/>
       <c r="C19" s="8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D19" s="29"/>
       <c r="E19" s="6"/>
@@ -1839,7 +1857,7 @@
         <f>B19</f>
         <v>0</v>
       </c>
-      <c r="J19" s="54"/>
+      <c r="J19" s="53"/>
       <c r="K19" s="15"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -1850,15 +1868,15 @@
       <c r="P19" s="16">
         <v>16</v>
       </c>
-      <c r="Q19" s="54"/>
+      <c r="Q19" s="53"/>
     </row>
     <row r="20" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B20" s="32"/>
       <c r="C20" s="8" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D20" s="33"/>
       <c r="E20" s="34"/>
@@ -1869,7 +1887,7 @@
         <f>B20</f>
         <v>0</v>
       </c>
-      <c r="J20" s="54"/>
+      <c r="J20" s="53"/>
       <c r="K20" s="15"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -1878,12 +1896,12 @@
       <c r="P20" s="16">
         <v>15</v>
       </c>
-      <c r="Q20" s="54"/>
+      <c r="Q20" s="53"/>
     </row>
     <row r="21" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="58"/>
-      <c r="B21" s="58"/>
-      <c r="C21" s="60"/>
+      <c r="A21" s="54"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="56"/>
       <c r="D21" s="30">
         <f t="shared" ref="D21:I21" si="1">((K7*D7)+(K8*D8)+(K9*D9)+(K10*D10)+(D11*K11)+(K12*D12)+(K13*D13)+(K14*D14)+(K15*D15)+(K16*D16)+(K17*D17)+(K18*D18)+(K19*D19)+(K20*D20))/K21</f>
         <v>0</v>
@@ -1908,7 +1926,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J21" s="54"/>
+      <c r="J21" s="53"/>
       <c r="K21" s="17">
         <v>60</v>
       </c>
@@ -1927,11 +1945,11 @@
       <c r="P21" s="19">
         <v>60</v>
       </c>
-      <c r="Q21" s="54"/>
+      <c r="Q21" s="53"/>
     </row>
     <row r="22" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B22" s="6">
         <f>SUM(D22:I22)/6</f>
@@ -1962,7 +1980,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J22" s="54"/>
+      <c r="J22" s="53"/>
       <c r="K22" s="3">
         <v>100</v>
       </c>
@@ -1981,132 +1999,132 @@
       <c r="P22" s="5">
         <v>100</v>
       </c>
-      <c r="Q22" s="54"/>
+      <c r="Q22" s="53"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="54"/>
-      <c r="B23" s="54"/>
-      <c r="C23" s="54"/>
-      <c r="D23" s="54"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="54"/>
-      <c r="H23" s="54"/>
-      <c r="I23" s="54"/>
-      <c r="J23" s="54"/>
-      <c r="K23" s="54"/>
-      <c r="L23" s="54"/>
-      <c r="M23" s="54"/>
-      <c r="N23" s="54"/>
-      <c r="O23" s="54"/>
-      <c r="P23" s="54"/>
-      <c r="Q23" s="54"/>
+      <c r="A23" s="53"/>
+      <c r="B23" s="53"/>
+      <c r="C23" s="53"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="53"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="53"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="53"/>
+      <c r="L23" s="53"/>
+      <c r="M23" s="53"/>
+      <c r="N23" s="53"/>
+      <c r="O23" s="53"/>
+      <c r="P23" s="53"/>
+      <c r="Q23" s="53"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="54"/>
-      <c r="B24" s="54"/>
-      <c r="C24" s="54"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="54"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="54"/>
-      <c r="J24" s="54"/>
-      <c r="K24" s="54"/>
-      <c r="L24" s="54"/>
-      <c r="M24" s="54"/>
-      <c r="N24" s="54"/>
-      <c r="O24" s="54"/>
-      <c r="P24" s="54"/>
-      <c r="Q24" s="54"/>
+      <c r="A24" s="53"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="53"/>
+      <c r="K24" s="53"/>
+      <c r="L24" s="53"/>
+      <c r="M24" s="53"/>
+      <c r="N24" s="53"/>
+      <c r="O24" s="53"/>
+      <c r="P24" s="53"/>
+      <c r="Q24" s="53"/>
     </row>
     <row r="25" spans="1:17" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A25" s="53" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" s="53"/>
-      <c r="C25" s="53"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="53"/>
-      <c r="F25" s="53"/>
-      <c r="G25" s="53"/>
-      <c r="H25" s="53"/>
-      <c r="I25" s="53"/>
-      <c r="J25" s="53"/>
-      <c r="K25" s="53"/>
-      <c r="L25" s="53"/>
-      <c r="M25" s="53"/>
-      <c r="N25" s="53"/>
-      <c r="O25" s="53"/>
-      <c r="P25" s="53"/>
-      <c r="Q25" s="54"/>
+      <c r="A25" s="59" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" s="59"/>
+      <c r="C25" s="59"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="59"/>
+      <c r="J25" s="59"/>
+      <c r="K25" s="59"/>
+      <c r="L25" s="59"/>
+      <c r="M25" s="59"/>
+      <c r="N25" s="59"/>
+      <c r="O25" s="59"/>
+      <c r="P25" s="59"/>
+      <c r="Q25" s="53"/>
     </row>
     <row r="26" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="42"/>
       <c r="B26" s="42"/>
-      <c r="C26" s="54"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="54"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="54"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="54"/>
-      <c r="J26" s="54"/>
-      <c r="K26" s="54"/>
-      <c r="L26" s="54"/>
-      <c r="M26" s="54"/>
-      <c r="N26" s="54"/>
-      <c r="O26" s="54"/>
-      <c r="P26" s="54"/>
-      <c r="Q26" s="54"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="53"/>
+      <c r="M26" s="53"/>
+      <c r="N26" s="53"/>
+      <c r="O26" s="53"/>
+      <c r="P26" s="53"/>
+      <c r="Q26" s="53"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="42"/>
       <c r="B27" s="42"/>
       <c r="D27" s="9" t="s">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="J27" s="54"/>
+        <v>76</v>
+      </c>
+      <c r="J27" s="53"/>
       <c r="K27" s="9" t="s">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="M27" s="10" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="P27" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q27" s="54"/>
+        <v>76</v>
+      </c>
+      <c r="Q27" s="53"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="42"/>
       <c r="B28" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C28" s="43"/>
       <c r="D28" s="25">
@@ -2133,7 +2151,7 @@
         <f>C28</f>
         <v>0</v>
       </c>
-      <c r="J28" s="54"/>
+      <c r="J28" s="53"/>
       <c r="K28" s="12">
         <v>15</v>
       </c>
@@ -2152,12 +2170,12 @@
       <c r="P28" s="14">
         <v>15</v>
       </c>
-      <c r="Q28" s="54"/>
+      <c r="Q28" s="53"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="42"/>
       <c r="B29" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C29" s="43"/>
       <c r="D29" s="23">
@@ -2184,7 +2202,7 @@
         <f>C29</f>
         <v>0</v>
       </c>
-      <c r="J29" s="54"/>
+      <c r="J29" s="53"/>
       <c r="K29" s="15">
         <v>5</v>
       </c>
@@ -2203,12 +2221,12 @@
       <c r="P29" s="16">
         <v>5</v>
       </c>
-      <c r="Q29" s="54"/>
+      <c r="Q29" s="53"/>
     </row>
     <row r="30" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="42"/>
       <c r="B30" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C30" s="43"/>
       <c r="D30" s="50">
@@ -2235,7 +2253,7 @@
         <f>C30</f>
         <v>0</v>
       </c>
-      <c r="J30" s="54"/>
+      <c r="J30" s="53"/>
       <c r="K30" s="17">
         <v>40</v>
       </c>
@@ -2254,7 +2272,7 @@
       <c r="P30" s="19">
         <v>40</v>
       </c>
-      <c r="Q30" s="54"/>
+      <c r="Q30" s="53"/>
     </row>
     <row r="31" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="36"/>
@@ -2284,7 +2302,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J31" s="54"/>
+      <c r="J31" s="53"/>
       <c r="K31" s="47">
         <v>60</v>
       </c>
@@ -2303,38 +2321,38 @@
       <c r="P31" s="49">
         <v>60</v>
       </c>
-      <c r="Q31" s="54"/>
+      <c r="Q31" s="53"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C32" s="57"/>
-      <c r="D32" s="54"/>
-      <c r="E32" s="54"/>
-      <c r="F32" s="54"/>
-      <c r="G32" s="54"/>
-      <c r="H32" s="54"/>
-      <c r="I32" s="54"/>
-      <c r="J32" s="54"/>
-      <c r="K32" s="56"/>
-      <c r="L32" s="56"/>
-      <c r="M32" s="56"/>
-      <c r="N32" s="56"/>
-      <c r="O32" s="56"/>
-      <c r="P32" s="56"/>
-      <c r="Q32" s="54"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="53"/>
+      <c r="G32" s="53"/>
+      <c r="H32" s="53"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="58"/>
+      <c r="L32" s="58"/>
+      <c r="M32" s="58"/>
+      <c r="N32" s="58"/>
+      <c r="O32" s="58"/>
+      <c r="P32" s="58"/>
+      <c r="Q32" s="53"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B33" s="32"/>
       <c r="C33" s="8" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D33" s="25">
         <f>$B33</f>
@@ -2351,7 +2369,7 @@
         <f>$B33</f>
         <v>0</v>
       </c>
-      <c r="J33" s="54"/>
+      <c r="J33" s="53"/>
       <c r="K33" s="12">
         <v>16</v>
       </c>
@@ -2364,15 +2382,15 @@
       <c r="P33" s="14">
         <v>4</v>
       </c>
-      <c r="Q33" s="54"/>
+      <c r="Q33" s="53"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B34" s="32"/>
       <c r="C34" s="8" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D34" s="23">
         <f>$B34</f>
@@ -2386,7 +2404,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="26"/>
-      <c r="J34" s="54"/>
+      <c r="J34" s="53"/>
       <c r="K34" s="15">
         <v>8</v>
       </c>
@@ -2397,15 +2415,15 @@
         <v>10</v>
       </c>
       <c r="P34" s="16"/>
-      <c r="Q34" s="54"/>
+      <c r="Q34" s="53"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B35" s="32"/>
       <c r="C35" s="8" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D35" s="29"/>
       <c r="E35" s="6"/>
@@ -2416,7 +2434,7 @@
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="26"/>
-      <c r="J35" s="54"/>
+      <c r="J35" s="53"/>
       <c r="K35" s="15"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -2425,15 +2443,15 @@
       </c>
       <c r="O35" s="1"/>
       <c r="P35" s="16"/>
-      <c r="Q35" s="54"/>
+      <c r="Q35" s="53"/>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B36" s="32"/>
       <c r="C36" s="8" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D36" s="29"/>
       <c r="E36" s="6">
@@ -2444,7 +2462,7 @@
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
       <c r="I36" s="26"/>
-      <c r="J36" s="54"/>
+      <c r="J36" s="53"/>
       <c r="K36" s="15"/>
       <c r="L36" s="1">
         <v>12</v>
@@ -2453,15 +2471,15 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
       <c r="P36" s="16"/>
-      <c r="Q36" s="54"/>
+      <c r="Q36" s="53"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B37" s="32"/>
       <c r="C37" s="8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D37" s="29"/>
       <c r="E37" s="6">
@@ -2475,7 +2493,7 @@
         <f>$B37</f>
         <v>0</v>
       </c>
-      <c r="J37" s="54"/>
+      <c r="J37" s="53"/>
       <c r="K37" s="15"/>
       <c r="L37" s="1">
         <v>4</v>
@@ -2486,15 +2504,15 @@
       <c r="P37" s="16">
         <v>13</v>
       </c>
-      <c r="Q37" s="54"/>
+      <c r="Q37" s="53"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B38" s="32"/>
       <c r="C38" s="8" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D38" s="29"/>
       <c r="E38" s="6"/>
@@ -2508,7 +2526,7 @@
         <f>B38</f>
         <v>0</v>
       </c>
-      <c r="J38" s="54"/>
+      <c r="J38" s="53"/>
       <c r="K38" s="15"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -2519,15 +2537,15 @@
       <c r="P38" s="16">
         <v>13</v>
       </c>
-      <c r="Q38" s="54"/>
+      <c r="Q38" s="53"/>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B39" s="32"/>
       <c r="C39" s="8" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D39" s="29"/>
       <c r="E39" s="6"/>
@@ -2538,7 +2556,7 @@
         <f>$B39</f>
         <v>0</v>
       </c>
-      <c r="J39" s="54"/>
+      <c r="J39" s="53"/>
       <c r="K39" s="15"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -2547,15 +2565,15 @@
       <c r="P39" s="16">
         <v>10</v>
       </c>
-      <c r="Q39" s="54"/>
+      <c r="Q39" s="53"/>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B40" s="32"/>
       <c r="C40" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D40" s="29"/>
       <c r="E40" s="6"/>
@@ -2566,7 +2584,7 @@
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
       <c r="I40" s="26"/>
-      <c r="J40" s="54"/>
+      <c r="J40" s="53"/>
       <c r="K40" s="15"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1">
@@ -2575,15 +2593,15 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
       <c r="P40" s="16"/>
-      <c r="Q40" s="54"/>
+      <c r="Q40" s="53"/>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B41" s="32"/>
       <c r="C41" s="8" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D41" s="29"/>
       <c r="E41" s="6">
@@ -2597,7 +2615,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="26"/>
-      <c r="J41" s="54"/>
+      <c r="J41" s="53"/>
       <c r="K41" s="15"/>
       <c r="L41" s="1">
         <v>4</v>
@@ -2608,15 +2626,15 @@
         <v>22</v>
       </c>
       <c r="P41" s="16"/>
-      <c r="Q41" s="54"/>
+      <c r="Q41" s="53"/>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B42" s="32"/>
       <c r="C42" s="8" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D42" s="23">
         <f>$B42</f>
@@ -2636,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="26"/>
-      <c r="J42" s="54"/>
+      <c r="J42" s="53"/>
       <c r="K42" s="15">
         <v>8</v>
       </c>
@@ -2651,15 +2669,15 @@
         <v>4</v>
       </c>
       <c r="P42" s="16"/>
-      <c r="Q42" s="54"/>
+      <c r="Q42" s="53"/>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B43" s="32"/>
       <c r="C43" s="8" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D43" s="29">
         <f>B43</f>
@@ -2679,7 +2697,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="26"/>
-      <c r="J43" s="54"/>
+      <c r="J43" s="53"/>
       <c r="K43" s="15">
         <v>8</v>
       </c>
@@ -2694,15 +2712,15 @@
         <v>4</v>
       </c>
       <c r="P43" s="16"/>
-      <c r="Q43" s="54"/>
+      <c r="Q43" s="53"/>
     </row>
     <row r="44" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B44" s="32"/>
       <c r="C44" s="8" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D44" s="33"/>
       <c r="E44" s="34">
@@ -2713,7 +2731,7 @@
       <c r="G44" s="34"/>
       <c r="H44" s="34"/>
       <c r="I44" s="35"/>
-      <c r="J44" s="54"/>
+      <c r="J44" s="53"/>
       <c r="K44" s="15"/>
       <c r="L44" s="1">
         <v>12</v>
@@ -2722,12 +2740,12 @@
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="16"/>
-      <c r="Q44" s="54"/>
+      <c r="Q44" s="53"/>
     </row>
     <row r="45" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="58"/>
-      <c r="B45" s="58"/>
-      <c r="C45" s="58"/>
+      <c r="A45" s="54"/>
+      <c r="B45" s="54"/>
+      <c r="C45" s="54"/>
       <c r="D45" s="30">
         <f t="shared" ref="D45:I45" si="4">((K33*D33)+(K34*D34)+(D35*K35)+(K36*D36)+(K37*D37)+(K38*D38)+(K39*D39)+(K40*D40)+(K41*D41)+(K42*D42)+(K43*D43)+(K44*D44))/K45</f>
         <v>0</v>
@@ -2752,7 +2770,7 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J45" s="54"/>
+      <c r="J45" s="53"/>
       <c r="K45" s="17">
         <v>40</v>
       </c>
@@ -2771,11 +2789,11 @@
       <c r="P45" s="19">
         <v>40</v>
       </c>
-      <c r="Q45" s="54"/>
+      <c r="Q45" s="53"/>
     </row>
     <row r="46" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B46" s="6">
         <f>SUM(D46:I46)/6</f>
@@ -2806,7 +2824,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J46" s="54"/>
+      <c r="J46" s="53"/>
       <c r="K46" s="3">
         <v>100</v>
       </c>
@@ -2825,159 +2843,159 @@
       <c r="P46" s="5">
         <v>100</v>
       </c>
-      <c r="Q46" s="54"/>
+      <c r="Q46" s="53"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" s="54"/>
-      <c r="B47" s="54"/>
-      <c r="C47" s="54"/>
-      <c r="D47" s="54"/>
-      <c r="E47" s="54"/>
-      <c r="F47" s="54"/>
-      <c r="G47" s="54"/>
-      <c r="H47" s="54"/>
-      <c r="I47" s="54"/>
-      <c r="J47" s="54"/>
-      <c r="K47" s="54"/>
-      <c r="L47" s="54"/>
-      <c r="M47" s="54"/>
-      <c r="N47" s="54"/>
-      <c r="O47" s="54"/>
-      <c r="P47" s="54"/>
-      <c r="Q47" s="54"/>
+      <c r="A47" s="53"/>
+      <c r="B47" s="53"/>
+      <c r="C47" s="53"/>
+      <c r="D47" s="53"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="53"/>
+      <c r="G47" s="53"/>
+      <c r="H47" s="53"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="53"/>
+      <c r="K47" s="53"/>
+      <c r="L47" s="53"/>
+      <c r="M47" s="53"/>
+      <c r="N47" s="53"/>
+      <c r="O47" s="53"/>
+      <c r="P47" s="53"/>
+      <c r="Q47" s="53"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="54"/>
-      <c r="B48" s="54"/>
-      <c r="C48" s="54"/>
-      <c r="D48" s="54"/>
-      <c r="E48" s="54"/>
-      <c r="F48" s="54"/>
-      <c r="G48" s="54"/>
-      <c r="H48" s="54"/>
-      <c r="I48" s="54"/>
-      <c r="J48" s="54"/>
-      <c r="K48" s="54"/>
-      <c r="L48" s="54"/>
-      <c r="M48" s="54"/>
-      <c r="N48" s="54"/>
-      <c r="O48" s="54"/>
-      <c r="P48" s="54"/>
-      <c r="Q48" s="54"/>
+      <c r="A48" s="53"/>
+      <c r="B48" s="53"/>
+      <c r="C48" s="53"/>
+      <c r="D48" s="53"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="53"/>
+      <c r="G48" s="53"/>
+      <c r="H48" s="53"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="53"/>
+      <c r="L48" s="53"/>
+      <c r="M48" s="53"/>
+      <c r="N48" s="53"/>
+      <c r="O48" s="53"/>
+      <c r="P48" s="53"/>
+      <c r="Q48" s="53"/>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="54"/>
-      <c r="B49" s="54"/>
-      <c r="C49" s="54"/>
-      <c r="D49" s="54"/>
-      <c r="E49" s="54"/>
-      <c r="F49" s="54"/>
-      <c r="G49" s="54"/>
-      <c r="H49" s="54"/>
-      <c r="I49" s="54"/>
-      <c r="J49" s="54"/>
-      <c r="K49" s="54"/>
-      <c r="L49" s="54"/>
-      <c r="M49" s="54"/>
-      <c r="N49" s="54"/>
-      <c r="O49" s="54"/>
-      <c r="P49" s="54"/>
-      <c r="Q49" s="54"/>
+      <c r="A49" s="53"/>
+      <c r="B49" s="53"/>
+      <c r="C49" s="53"/>
+      <c r="D49" s="53"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="53"/>
+      <c r="G49" s="53"/>
+      <c r="H49" s="53"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="53"/>
+      <c r="L49" s="53"/>
+      <c r="M49" s="53"/>
+      <c r="N49" s="53"/>
+      <c r="O49" s="53"/>
+      <c r="P49" s="53"/>
+      <c r="Q49" s="53"/>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A50" s="54"/>
-      <c r="B50" s="54"/>
-      <c r="C50" s="54"/>
-      <c r="D50" s="54"/>
-      <c r="E50" s="54"/>
-      <c r="F50" s="54"/>
-      <c r="G50" s="54"/>
-      <c r="H50" s="54"/>
-      <c r="I50" s="54"/>
-      <c r="J50" s="54"/>
-      <c r="K50" s="54"/>
-      <c r="L50" s="54"/>
-      <c r="M50" s="54"/>
-      <c r="N50" s="54"/>
-      <c r="O50" s="54"/>
-      <c r="P50" s="54"/>
-      <c r="Q50" s="54"/>
+      <c r="A50" s="53"/>
+      <c r="B50" s="53"/>
+      <c r="C50" s="53"/>
+      <c r="D50" s="53"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="53"/>
+      <c r="G50" s="53"/>
+      <c r="H50" s="53"/>
+      <c r="I50" s="53"/>
+      <c r="J50" s="53"/>
+      <c r="K50" s="53"/>
+      <c r="L50" s="53"/>
+      <c r="M50" s="53"/>
+      <c r="N50" s="53"/>
+      <c r="O50" s="53"/>
+      <c r="P50" s="53"/>
+      <c r="Q50" s="53"/>
     </row>
     <row r="51" spans="1:17" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A51" s="53" t="s">
-        <v>13</v>
-      </c>
-      <c r="B51" s="53"/>
-      <c r="C51" s="53"/>
-      <c r="D51" s="53"/>
-      <c r="E51" s="53"/>
-      <c r="F51" s="53"/>
-      <c r="G51" s="53"/>
-      <c r="H51" s="53"/>
-      <c r="I51" s="53"/>
-      <c r="J51" s="53"/>
-      <c r="K51" s="53"/>
-      <c r="L51" s="53"/>
-      <c r="M51" s="53"/>
-      <c r="N51" s="53"/>
-      <c r="O51" s="53"/>
-      <c r="P51" s="53"/>
-      <c r="Q51" s="54"/>
+      <c r="A51" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B51" s="59"/>
+      <c r="C51" s="59"/>
+      <c r="D51" s="59"/>
+      <c r="E51" s="59"/>
+      <c r="F51" s="59"/>
+      <c r="G51" s="59"/>
+      <c r="H51" s="59"/>
+      <c r="I51" s="59"/>
+      <c r="J51" s="59"/>
+      <c r="K51" s="59"/>
+      <c r="L51" s="59"/>
+      <c r="M51" s="59"/>
+      <c r="N51" s="59"/>
+      <c r="O51" s="59"/>
+      <c r="P51" s="59"/>
+      <c r="Q51" s="53"/>
     </row>
     <row r="52" spans="1:17" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="59"/>
-      <c r="B52" s="59"/>
-      <c r="C52" s="59"/>
-      <c r="D52" s="59"/>
-      <c r="E52" s="59"/>
-      <c r="F52" s="59"/>
-      <c r="G52" s="59"/>
-      <c r="H52" s="59"/>
-      <c r="I52" s="59"/>
-      <c r="J52" s="59"/>
-      <c r="K52" s="59"/>
-      <c r="L52" s="59"/>
-      <c r="M52" s="59"/>
-      <c r="N52" s="59"/>
-      <c r="O52" s="59"/>
-      <c r="P52" s="59"/>
-      <c r="Q52" s="54"/>
+      <c r="A52" s="55"/>
+      <c r="B52" s="55"/>
+      <c r="C52" s="55"/>
+      <c r="D52" s="55"/>
+      <c r="E52" s="55"/>
+      <c r="F52" s="55"/>
+      <c r="G52" s="55"/>
+      <c r="H52" s="55"/>
+      <c r="I52" s="55"/>
+      <c r="J52" s="55"/>
+      <c r="K52" s="55"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="55"/>
+      <c r="N52" s="55"/>
+      <c r="O52" s="55"/>
+      <c r="P52" s="55"/>
+      <c r="Q52" s="53"/>
     </row>
     <row r="53" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="54"/>
-      <c r="B53" s="54"/>
-      <c r="C53" s="54"/>
+      <c r="A53" s="53"/>
+      <c r="B53" s="53"/>
+      <c r="C53" s="53"/>
       <c r="D53" s="3" t="s">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J53" s="54"/>
-      <c r="K53" s="54"/>
-      <c r="L53" s="54"/>
-      <c r="M53" s="54"/>
-      <c r="N53" s="54"/>
-      <c r="O53" s="54"/>
-      <c r="P53" s="54"/>
-      <c r="Q53" s="54"/>
+        <v>70</v>
+      </c>
+      <c r="J53" s="53"/>
+      <c r="K53" s="53"/>
+      <c r="L53" s="53"/>
+      <c r="M53" s="53"/>
+      <c r="N53" s="53"/>
+      <c r="O53" s="53"/>
+      <c r="P53" s="53"/>
+      <c r="Q53" s="53"/>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A54" s="54"/>
-      <c r="B54" s="54"/>
-      <c r="C54" s="54"/>
+      <c r="A54" s="53"/>
+      <c r="B54" s="53"/>
+      <c r="C54" s="53"/>
       <c r="D54" s="1">
         <f t="shared" ref="D54:I54" si="6">(D46+D22)/2</f>
         <v>0</v>
@@ -3002,55 +3020,60 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J54" s="54"/>
-      <c r="K54" s="54"/>
-      <c r="L54" s="54"/>
-      <c r="M54" s="54"/>
-      <c r="N54" s="54"/>
-      <c r="O54" s="54"/>
-      <c r="P54" s="54"/>
-      <c r="Q54" s="54"/>
+      <c r="J54" s="53"/>
+      <c r="K54" s="53"/>
+      <c r="L54" s="53"/>
+      <c r="M54" s="53"/>
+      <c r="N54" s="53"/>
+      <c r="O54" s="53"/>
+      <c r="P54" s="53"/>
+      <c r="Q54" s="53"/>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A55" s="54"/>
-      <c r="B55" s="54"/>
-      <c r="C55" s="54"/>
-      <c r="D55" s="54"/>
-      <c r="E55" s="54"/>
-      <c r="F55" s="54"/>
-      <c r="G55" s="54"/>
-      <c r="H55" s="54"/>
-      <c r="I55" s="54"/>
-      <c r="J55" s="54"/>
-      <c r="K55" s="54"/>
-      <c r="L55" s="54"/>
-      <c r="M55" s="54"/>
-      <c r="N55" s="54"/>
-      <c r="O55" s="54"/>
-      <c r="P55" s="54"/>
-      <c r="Q55" s="54"/>
+      <c r="A55" s="53"/>
+      <c r="B55" s="53"/>
+      <c r="C55" s="53"/>
+      <c r="D55" s="53"/>
+      <c r="E55" s="53"/>
+      <c r="F55" s="53"/>
+      <c r="G55" s="53"/>
+      <c r="H55" s="53"/>
+      <c r="I55" s="53"/>
+      <c r="J55" s="53"/>
+      <c r="K55" s="53"/>
+      <c r="L55" s="53"/>
+      <c r="M55" s="53"/>
+      <c r="N55" s="53"/>
+      <c r="O55" s="53"/>
+      <c r="P55" s="53"/>
+      <c r="Q55" s="53"/>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A56" s="54"/>
-      <c r="B56" s="54"/>
-      <c r="C56" s="54"/>
-      <c r="D56" s="54"/>
-      <c r="E56" s="54"/>
-      <c r="F56" s="54"/>
-      <c r="G56" s="54"/>
-      <c r="H56" s="54"/>
-      <c r="I56" s="54"/>
-      <c r="J56" s="54"/>
-      <c r="K56" s="54"/>
-      <c r="L56" s="54"/>
-      <c r="M56" s="54"/>
-      <c r="N56" s="54"/>
-      <c r="O56" s="54"/>
-      <c r="P56" s="54"/>
-      <c r="Q56" s="54"/>
+      <c r="A56" s="53"/>
+      <c r="B56" s="53"/>
+      <c r="C56" s="53"/>
+      <c r="D56" s="53"/>
+      <c r="E56" s="53"/>
+      <c r="F56" s="53"/>
+      <c r="G56" s="53"/>
+      <c r="H56" s="53"/>
+      <c r="I56" s="53"/>
+      <c r="J56" s="53"/>
+      <c r="K56" s="53"/>
+      <c r="L56" s="53"/>
+      <c r="M56" s="53"/>
+      <c r="N56" s="53"/>
+      <c r="O56" s="53"/>
+      <c r="P56" s="53"/>
+      <c r="Q56" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A51:P51"/>
+    <mergeCell ref="J3:J22"/>
+    <mergeCell ref="A2:B5"/>
+    <mergeCell ref="K6:P6"/>
+    <mergeCell ref="C6:I6"/>
     <mergeCell ref="Q1:Q56"/>
     <mergeCell ref="A47:P50"/>
     <mergeCell ref="A45:C45"/>
@@ -3067,11 +3090,6 @@
     <mergeCell ref="K32:P32"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A25:P25"/>
-    <mergeCell ref="A51:P51"/>
-    <mergeCell ref="J3:J22"/>
-    <mergeCell ref="A2:B5"/>
-    <mergeCell ref="K6:P6"/>
-    <mergeCell ref="C6:I6"/>
   </mergeCells>
   <conditionalFormatting sqref="D22:I22">
     <cfRule type="colorScale" priority="5">
